--- a/embedding_reranking_api_mapping.xlsx
+++ b/embedding_reranking_api_mapping.xlsx
@@ -1,68 +1,191 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inkwon/Documents/Work/13. Automation/36. SDS LCS AN/AIOps - OpsGuardian/skeleton-code/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15F20C9-9A08-944F-97FC-BBAE302B982D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1040" yWindow="660" windowWidth="33520" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embedding &amp; Rerank Mapping" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Embedding &amp; Rerank Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>Embedding / Reranking API mapping — please fill the two YELLOW columns (D, E) with the customer's server request/response. The two BLUE columns (B, C) show exactly what OpsG (network_rca_backend) sends/expects today. Once filled, we will implement the translation inside the adapter.</t>
+  </si>
+  <si>
+    <t>OpsG side (network_rca_backend -&gt; adapter)  [reference, do not change]</t>
+  </si>
+  <si>
+    <t>Customer server side (adapter -&gt; customer)  [PLEASE FILL]</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>OpsG Request (what we send)</t>
+  </si>
+  <si>
+    <t>OpsG Response (what we expect back)</t>
+  </si>
+  <si>
+    <t>Customer Request (FILL)</t>
+  </si>
+  <si>
+    <t>Customer Response (FILL)</t>
+  </si>
+  <si>
+    <t>Embedding</t>
+  </si>
+  <si>
+    <t>POST  /v1/embeddings
+Content-Type: application/json
+{
+  "model": "bge-m3",
+  "input": ["text 1", "text 2", "..."]   // string or array of strings
+}
+Note: the semantic-splitter path also posts {"sentences": ["..."]} to the
+same embedding endpoint; both variants expect data[].embedding in the response.</t>
+  </si>
+  <si>
+    <t>{
+  "data": [
+    {"index": 0, "object": "embedding", "embedding": [0.012, -0.034, ...]},
+    {"index": 1, "object": "embedding", "embedding": [...]}
+  ],
+  "model": "bge-m3",
+  "usage": { ... }
+}
+OpsG reads: data[i].embedding, aligned to input order.</t>
+  </si>
+  <si>
+    <t>Reranking</t>
+  </si>
+  <si>
+    <t>POST  /score
+Content-Type: application/json
+{
+  "model": "bge-reranker-v2-m3",
+  "text_1": "the query string",
+  "text_2": ["candidate doc 1", "candidate doc 2", "..."]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "data": [
+    {"index": 0, "object": "score", "score": 0.9975},
+    {"index": 1, "object": "score", "score": 0.0000248}
+  ]
+}
+OpsG reads: data[i].score, aligned to text_2 order.</t>
+  </si>
+  <si>
+    <t>Also please confirm:
+  1) Exact endpoint paths on the customer server (embedding = /v1/embeddings ?  rerank = /v1/rerank ?).
+  2) For rerank: the request field names (query/documents? top_n?) and the score field name + whether
+     results are returned sorted or in original input order (OpsG needs scores aligned to text_2 order).
+  3) Transport: is the customer server HTTP or HTTPS, and does it require a client certificate (mTLS)?
+     (This is handled by the adapter, not OpsG — we just need to configure it.)</t>
+  </si>
+  <si>
+    <t>POST /v1/embeddings
+Content-Type: application/json
+{
+  "model": "bge-m3"
+  " input": ["apple", "banana"]
+}</t>
+  </si>
+  <si>
+    <t>please find the "test_embedding.json"</t>
+  </si>
+  <si>
+    <t>POST /v1/rerank
+Content-Type: application/json
+{
+  "model": "bge-reranker",
+  "query": "what is stronger",
+  "documents": ["Cat","Mouse","Cheeze"]
+}</t>
+  </si>
+  <si>
+    <t>please find the "test_reranking.json"</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,122 +199,65 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="FF999999"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="FF999999"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="FF999999"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="FF999999"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -479,144 +545,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Embedding / Reranking API mapping — please fill the two YELLOW columns (D, E) with the customer's server request/response. The two BLUE columns (B, C) show exactly what OpsG (network_rca_backend) sends/expects today. Once filled, we will implement the translation inside the adapter.</t>
-        </is>
-      </c>
+    <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>OpsG side (network_rca_backend -&gt; adapter)  [reference, do not change]</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Customer server side (adapter -&gt; customer)  [PLEASE FILL]</t>
-        </is>
-      </c>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6"/>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>OpsG Request (what we send)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>OpsG Response (what we expect back)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Customer Request (FILL)</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Customer Response (FILL)</t>
-        </is>
+    <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" ht="180" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Embedding</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>POST  /v1/embeddings
-Content-Type: application/json
-{
-  "model": "bge-m3",
-  "input": ["text 1", "text 2", "..."]   // string or array of strings
-}
-Note: the semantic-splitter path also posts {"sentences": ["..."]} to the
-same embedding endpoint; both variants expect data[].embedding in the response.</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>{
-  "data": [
-    {"index": 0, "object": "embedding", "embedding": [0.012, -0.034, ...]},
-    {"index": 1, "object": "embedding", "embedding": [...]}
-  ],
-  "model": "bge-m3",
-  "usage": { ... }
-}
-OpsG reads: data[i].embedding, aligned to input order.</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
+    <row r="4" spans="1:5" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" ht="180" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Reranking</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>POST  /score
-Content-Type: application/json
-{
-  "model": "bge-reranker-v2-m3",
-  "text_1": "the query string",
-  "text_2": ["candidate doc 1", "candidate doc 2", "..."]
-}</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>{
-  "data": [
-    {"index": 0, "object": "score", "score": 0.9975},
-    {"index": 1, "object": "score", "score": 0.0000248}
-  ]
-}
-OpsG reads: data[i].score, aligned to text_2 order.</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
+    <row r="5" spans="1:5" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Also please confirm:
-  1) Exact endpoint paths on the customer server (embedding = /v1/embeddings ?  rerank = /v1/rerank ?).
-  2) For rerank: the request field names (query/documents? top_n?) and the score field name + whether
-     results are returned sorted or in original input order (OpsG needs scores aligned to text_2 order).
-  3) Transport: is the customer server HTTP or HTTPS, and does it require a client certificate (mTLS)?
-     (This is handled by the adapter, not OpsG — we just need to configure it.)</t>
-        </is>
-      </c>
+    <row r="6" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -626,5 +641,14 @@
     <mergeCell ref="D2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Cisco Confidential</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c8f49a32-fde3-48a5-9266-b5b0972a22dc}" enabled="1" method="Standard" siteId="{5ae1af62-9505-4097-a69a-c1553ef7840e}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>